--- a/Luban/Excel/临时角色.xlsx
+++ b/Luban/Excel/临时角色.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9060"/>
+    <workbookView windowWidth="22188" windowHeight="9060"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="11">
   <si>
     <t>主键</t>
   </si>
@@ -76,6 +76,9 @@
   </si>
   <si>
     <t>资源组</t>
+  </si>
+  <si>
+    <t>活动组</t>
   </si>
   <si>
     <t>Id</t>
@@ -765,7 +768,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -789,6 +792,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1107,8 +1113,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" outlineLevelRow="3" outlineLevelCol="5"/>
+  <dimension ref="A1:G4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" outlineLevelRow="3" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="9" style="2"/>
     <col min="2" max="2" width="14.2222222222222" style="2" customWidth="1"/>
@@ -1118,7 +1124,7 @@
     <col min="6" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="16.2" spans="1:6">
+    <row r="1" s="1" customFormat="1" ht="16.2" spans="1:7">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1135,36 +1141,41 @@
       <c r="F1" s="7" t="s">
         <v>4</v>
       </c>
+      <c r="G1" s="8" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="2" s="1" customFormat="1" ht="16.2" spans="1:6">
+    <row r="2" s="1" customFormat="1" ht="16.2" spans="1:7">
       <c r="A2" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="8" t="s">
         <v>6</v>
       </c>
+      <c r="B2" s="9" t="s">
+        <v>7</v>
+      </c>
       <c r="C2" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2" s="5"/>
       <c r="E2" s="6"/>
-      <c r="F2" s="9"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="8"/>
     </row>
-    <row r="3" s="1" customFormat="1" ht="16.2" spans="1:6">
+    <row r="3" s="1" customFormat="1" ht="16.2" spans="1:7">
       <c r="A3" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C3" s="4"/>
       <c r="D3" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E3" s="6"/>
       <c r="F3" s="7" t="s">
-        <v>9</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="G3" s="8"/>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="2">
